--- a/ablation_v1_comparison.xlsx
+++ b/ablation_v1_comparison.xlsx
@@ -496,22 +496,22 @@
         <v>-0.0279</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.008</v>
+        <v>0.5454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5858</v>
+        <v>0.419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5938</v>
+        <v>-0.1264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0386</v>
+        <v>0.4928</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6484</v>
+        <v>0.5272</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6098</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="3">
@@ -530,22 +530,22 @@
         <v>0.0042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5642</v>
+        <v>0.5059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06</v>
+        <v>0.5778</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5042</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5401</v>
+        <v>0.4527</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1196</v>
+        <v>0.5461</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4205</v>
+        <v>0.0934</v>
       </c>
     </row>
     <row r="4">
@@ -564,22 +564,22 @@
         <v>0.0177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6109</v>
+        <v>0.5014</v>
       </c>
       <c r="F4" t="n">
         <v>0.0289</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.582</v>
+        <v>-0.4725</v>
       </c>
       <c r="H4" t="n">
-        <v>0.819</v>
+        <v>0.7776</v>
       </c>
       <c r="I4" t="n">
         <v>0.0963</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7227</v>
+        <v>-0.6813</v>
       </c>
     </row>
     <row r="5">
@@ -598,22 +598,22 @@
         <v>0.0357</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4405</v>
+        <v>0.5542</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0868</v>
+        <v>0.4326</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3537</v>
+        <v>-0.1216</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6637</v>
+        <v>0.6932</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0344</v>
+        <v>0.3994</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6293</v>
+        <v>-0.2938</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +632,22 @@
         <v>0.0014</v>
       </c>
       <c r="E6" t="n">
-        <v>0.533</v>
+        <v>0.334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4111</v>
+        <v>0.0204</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1219</v>
+        <v>-0.3136</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2743</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3623</v>
+        <v>0.0326</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1523</v>
+        <v>-0.2417</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>0.0026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7133</v>
+        <v>0.5775</v>
       </c>
       <c r="F7" t="n">
-        <v>0.044</v>
+        <v>0.696</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6693</v>
+        <v>0.1185</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7245</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1094</v>
+        <v>0.7371</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6151</v>
+        <v>0.1469</v>
       </c>
     </row>
     <row r="8">
@@ -700,22 +700,22 @@
         <v>0.0824</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6445</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5376</v>
+        <v>0.5883</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1069</v>
+        <v>0.0192</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4142</v>
+        <v>0.4422</v>
       </c>
       <c r="I8" t="n">
-        <v>0.665</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2508</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.4694</v>
       </c>
       <c r="F9" t="n">
         <v>0.07969999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.3897</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0774</v>
+        <v>0.4419</v>
       </c>
       <c r="I9" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.3738</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         <v>0.015</v>
       </c>
       <c r="E10" t="n">
-        <v>0.646</v>
+        <v>0.6186</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6545</v>
+        <v>0.7134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0948</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5395</v>
+        <v>0.6574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5456</v>
+        <v>0.6708</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0061</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="11">
@@ -802,22 +802,22 @@
         <v>-0.0232</v>
       </c>
       <c r="E11" t="n">
-        <v>0.014</v>
+        <v>0.6106</v>
       </c>
       <c r="F11" t="n">
         <v>0.014</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.5966</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0166</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-0.0454</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0288</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -836,22 +836,22 @@
         <v>0.0118</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4238</v>
+        <v>0.5286</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2502</v>
+        <v>0.357</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1736</v>
+        <v>-0.1716</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4315</v>
+        <v>0.5461</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2604</v>
+        <v>0.3691</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1711</v>
+        <v>-0.177</v>
       </c>
     </row>
   </sheetData>
